--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
   <si>
     <t>Filename</t>
   </si>
@@ -808,682 +808,685 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9960,0.0008,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9929,0.0002,0.0001,0.0053</t>
-  </si>
-  <si>
-    <t>0.0119,0.0010,0.0009,0.9934</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0562,0.0005,0.0001,0.9762</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0002</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.9489,0.0016,0.0239,0.0004</t>
+  </si>
+  <si>
+    <t>0.0155,0.0008,0.9832,0.0005</t>
+  </si>
+  <si>
+    <t>0.5945,0.0004,0.5648,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0015,0.9967,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9968,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.2172,0.7863,0.0067,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9712,0.0002,0.0184,0.0002</t>
+  </si>
+  <si>
+    <t>0.5500,0.0029,0.2705,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9989,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.0001,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9984,0.0009</t>
+  </si>
+  <si>
+    <t>0.0177,0.9835,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9909,0.0060,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.8391,0.7412,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.5282,0.0005,0.3998,0.0003</t>
+  </si>
+  <si>
+    <t>0.2576,0.7360,0.0082,0.0022</t>
+  </si>
+  <si>
+    <t>0.0020,0.9945,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.0022,0.0768,0.9046,0.0032</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.0033,0.9917,0.0002</t>
+  </si>
+  <si>
+    <t>0.3360,0.0010,0.7752,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.0895,0.9824,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9960,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.8801,0.0001,0.9970</t>
+  </si>
+  <si>
+    <t>0.0266,0.9575,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0515,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0002,0.9965,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9881,0.0104,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0088,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9661,0.9717,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0100,0.9934,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0010,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.8133,0.0009,0.1795,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.0027,0.9977,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9698,0.2630,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.1609,0.0004,0.0111,0.8168</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.0014,0.9990</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0010,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9575,0.7694,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9586,0.9477,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9624,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0282,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9828,0.0003,0.0094,0.0001</t>
-  </si>
-  <si>
-    <t>0.0148,0.0006,0.9841,0.0013</t>
-  </si>
-  <si>
-    <t>0.1244,0.0011,0.9224,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.9875,0.0004,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9973,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.1542,0.8550,0.0135,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.9979,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9840,0.0002,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.0325,0.0017,0.9664,0.0010</t>
-  </si>
-  <si>
-    <t>0.0033,0.0004,0.9909,0.0019</t>
-  </si>
-  <si>
-    <t>0.0011,0.0008,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.3990,0.0001,0.7452,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.9969,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0458,0.9563,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.6625,0.0020,0.2022,0.0027</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0075</t>
-  </si>
-  <si>
-    <t>0.0069,0.9837,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0733,0.9422,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0069,0.9582,0.1316,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0828,0.9883,0.0008</t>
-  </si>
-  <si>
-    <t>0.0054,0.0021,0.9800,0.0035</t>
-  </si>
-  <si>
-    <t>0.0080,0.0108,0.9769,0.0003</t>
-  </si>
-  <si>
-    <t>0.9821,0.0000,0.0196,0.0000</t>
-  </si>
-  <si>
-    <t>0.0072,0.1786,0.9782,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9963,0.0078,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0023,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9512,0.0001,0.9919</t>
-  </si>
-  <si>
-    <t>0.0009,0.9971,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0521,0.9843,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.9964,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0013,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9878,0.0114,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0029,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9689,0.9326,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0024,0.9970,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.5927,0.0009,0.5454,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.0006,0.9961,0.0010</t>
-  </si>
-  <si>
-    <t>0.0006,0.0017,0.9982,0.0030</t>
-  </si>
-  <si>
-    <t>0.0001,0.9602,0.9706,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9735,0.9657,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0204,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9966,0.5611,0.0000</t>
-  </si>
-  <si>
-    <t>0.0105,0.0001,0.0348,0.9685</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0013,0.9991</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0048,0.9993</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9940,0.4173,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9910,0.2943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.4341,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.8227,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9963,0.0977,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0036,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0060,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0016,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.5802,0.0009,0.4901,0.0000</t>
-  </si>
-  <si>
-    <t>0.9838,0.0031,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.1184,0.0002,0.9290,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.9962,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0049,0.0001</t>
+    <t>0.9985,0.0017,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0040,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.0028,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0058,0.0001,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0108,0.9915,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.6305,0.3425,0.0218,0.0004</t>
+  </si>
+  <si>
+    <t>0.2848,0.0064,0.5573,0.0015</t>
+  </si>
+  <si>
+    <t>0.9720,0.0042,0.0078,0.0003</t>
+  </si>
+  <si>
+    <t>0.1219,0.0332,0.3978,0.0141</t>
+  </si>
+  <si>
+    <t>0.4643,0.0140,0.2760,0.0083</t>
+  </si>
+  <si>
+    <t>0.0006,0.9543,0.0076,0.5900</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9871,0.8315,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.9995,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3991,0.6383,0.0087,0.0003</t>
-  </si>
-  <si>
-    <t>0.9026,0.0185,0.0208,0.0039</t>
-  </si>
-  <si>
-    <t>0.9329,0.0101,0.0195,0.0005</t>
-  </si>
-  <si>
-    <t>0.1081,0.0242,0.4771,0.0246</t>
-  </si>
-  <si>
-    <t>0.4905,0.0028,0.4915,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.5063,0.0068,0.8679</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9977,0.3040,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.8567,0.1616,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.6540,0.3807,0.0055,0.0015</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.2039,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9843,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0892,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.0047,0.9916,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0477,0.0004,0.9406,0.0048</t>
-  </si>
-  <si>
-    <t>0.0092,0.0000,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0000,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0001,0.0000,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
+    <t>0.8749,0.1439,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.9371,0.0858,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9419,0.9760,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9389,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0039,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.4540,0.0012,0.6068,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0001,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9127,0.0005,0.0648,0.0003</t>
+  </si>
+  <si>
+    <t>0.7573,0.0000,0.4787,0.0000</t>
+  </si>
+  <si>
+    <t>0.9667,0.0009,0.0158,0.0003</t>
+  </si>
+  <si>
+    <t>0.2297,0.0002,0.0001,0.9422</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9370,0.0000</t>
-  </si>
-  <si>
-    <t>0.0180,0.9811,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0109,0.9882,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9802,0.0001,0.0001,0.0127</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0041,0.9982,0.0010</t>
-  </si>
-  <si>
-    <t>0.9977,0.0000,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0117,0.9780,0.0068,0.0008</t>
-  </si>
-  <si>
-    <t>0.9966,0.0021,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0009,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0104,0.9778,0.0067,0.0011</t>
-  </si>
-  <si>
-    <t>0.8722,0.0937,0.0020,0.0023</t>
-  </si>
-  <si>
-    <t>0.9976,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9937,0.0031,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9312,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9956,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0132,0.9877,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2903,0.0000,0.0000,0.9272</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0074,0.9989,0.0005</t>
+  </si>
+  <si>
+    <t>0.9929,0.0000,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.3485,0.4814,0.0218,0.0012</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9626,0.0308,0.0021,0.0023</t>
+  </si>
+  <si>
+    <t>0.0105,0.9844,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.7932,0.0281,0.1121,0.0022</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0001,0.0003</t>
   </si>
   <si>
     <t>0.9993,0.0001,0.0000,0.0002</t>
   </si>
   <si>
-    <t>0.9978,0.0027,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.7370,0.3403,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0223,0.9819,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.2593,0.4601,0.2181,0.0013</t>
-  </si>
-  <si>
-    <t>0.9838,0.0206,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8649,0.0713,0.0442,0.0027</t>
-  </si>
-  <si>
-    <t>0.0002,0.0079,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9109,0.0482,0.0335,0.0160</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0125,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0067,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0006,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.2136,0.0042,0.7237,0.0013</t>
-  </si>
-  <si>
-    <t>0.0033,0.0002,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0082,0.0025,0.9847,0.0016</t>
-  </si>
-  <si>
-    <t>0.0294,0.0295,0.9289,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.0019,0.9928,0.0004</t>
-  </si>
-  <si>
-    <t>0.1699,0.0011,0.8592,0.0006</t>
-  </si>
-  <si>
-    <t>0.3920,0.0026,0.3475,0.0118</t>
-  </si>
-  <si>
-    <t>0.1320,0.0032,0.8755,0.0024</t>
-  </si>
-  <si>
-    <t>0.0880,0.9496,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9992,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.7337,0.4123,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0288,0.9788,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.9961,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0017,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9874,0.0015,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.7508,0.0290,0.0922,0.0044</t>
-  </si>
-  <si>
-    <t>0.9697,0.0020,0.0109,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9953,0.0219</t>
-  </si>
-  <si>
-    <t>0.0035,0.0808,0.9588,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.0155,0.9961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0134,0.0025,0.9827,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9898,0.2230,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0057,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0009,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0144,0.9964,0.0011</t>
-  </si>
-  <si>
-    <t>0.0340,0.0296,0.8549,0.0113</t>
-  </si>
-  <si>
-    <t>0.3409,0.0007,0.6004,0.0016</t>
-  </si>
-  <si>
-    <t>0.0147,0.0002,0.9893,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9992,0.0010</t>
-  </si>
-  <si>
-    <t>0.0016,0.0315,0.9875,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0035,0.9948,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0009,0.9939,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9957,0.0016</t>
-  </si>
-  <si>
-    <t>0.7216,0.0022,0.1296,0.0073</t>
-  </si>
-  <si>
-    <t>0.7731,0.0000,0.3233,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0015,0.9965,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0105,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0009,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.1252,0.0009,0.8543,0.0038</t>
-  </si>
-  <si>
-    <t>0.0526,0.0109,0.8928,0.0007</t>
-  </si>
-  <si>
-    <t>0.0018,0.0012,0.9916,0.0019</t>
-  </si>
-  <si>
-    <t>0.9245,0.0002,0.0017,0.0420</t>
-  </si>
-  <si>
-    <t>0.0273,0.0118,0.0000,0.9852</t>
-  </si>
-  <si>
-    <t>0.0048,0.0000,0.0002,0.9980</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9603,0.0015,0.0001,0.0270</t>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9903,0.0132,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2390,0.8023,0.0070,0.0002</t>
+  </si>
+  <si>
+    <t>0.0313,0.9747,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.0096,0.5364,0.9332,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0013,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9631,0.0370,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0243,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.9833,0.0059,0.0033,0.0030</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0068,0.9874,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0009,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0129,0.0005,0.9819,0.0011</t>
+  </si>
+  <si>
+    <t>0.0172,0.0006,0.9846,0.0004</t>
+  </si>
+  <si>
+    <t>0.3547,0.0020,0.6586,0.0015</t>
+  </si>
+  <si>
+    <t>0.0427,0.0127,0.9111,0.0006</t>
+  </si>
+  <si>
+    <t>0.0229,0.3699,0.5585,0.0002</t>
+  </si>
+  <si>
+    <t>0.1163,0.0046,0.8439,0.0007</t>
+  </si>
+  <si>
+    <t>0.9758,0.0040,0.0035,0.0013</t>
+  </si>
+  <si>
+    <t>0.0204,0.0138,0.9454,0.0009</t>
+  </si>
+  <si>
+    <t>0.0054,0.9954,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9994,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9758,0.0399,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2099,0.8592,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.9975,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9832,0.0021,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9896,0.0007,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.7896,0.0080,0.1674,0.0020</t>
+  </si>
+  <si>
+    <t>0.9869,0.0013,0.0034,0.0004</t>
+  </si>
+  <si>
+    <t>0.0219,0.0009,0.9634,0.0077</t>
+  </si>
+  <si>
+    <t>0.0005,0.0048,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0269,0.9951,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.8475,0.7058,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9902,0.0080,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0048,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0461,0.6954,0.2119,0.0014</t>
+  </si>
+  <si>
+    <t>0.9145,0.0005,0.0345,0.0017</t>
+  </si>
+  <si>
+    <t>0.0303,0.0008,0.9841,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0024,0.9984,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.0429,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9988,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0039,0.0011,0.9888,0.0016</t>
+  </si>
+  <si>
+    <t>0.9715,0.0008,0.0110,0.0005</t>
+  </si>
+  <si>
+    <t>0.8376,0.0003,0.2272,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0017,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9872,0.0123,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.1730,0.8481,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.0042,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0196,0.9952,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0229,0.0007,0.9725,0.0015</t>
+  </si>
+  <si>
+    <t>0.0421,0.0040,0.9474,0.0010</t>
+  </si>
+  <si>
+    <t>0.0041,0.0005,0.9873,0.0024</t>
+  </si>
+  <si>
+    <t>0.9822,0.0002,0.0001,0.0122</t>
+  </si>
+  <si>
+    <t>0.0127,0.0318,0.0000,0.9882</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1883,7 +1886,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1897,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1911,7 +1914,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1925,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1939,7 +1942,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1953,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1967,7 +1970,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1981,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1995,7 +1998,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2009,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2023,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2037,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2051,7 +2054,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,10 +2065,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2079,7 +2082,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2093,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2107,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2121,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2135,7 +2138,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2149,7 +2152,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2163,7 +2166,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2177,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2188,10 +2191,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2205,7 +2208,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2219,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2233,7 +2236,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2247,7 +2250,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2261,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2275,7 +2278,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2289,7 +2292,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2303,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,10 +2317,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2331,7 +2334,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2345,7 +2348,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2359,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2373,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2387,7 +2390,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2401,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2415,7 +2418,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,10 +2429,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2443,7 +2446,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2457,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2471,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,10 +2485,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2499,7 +2502,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2513,7 +2516,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2527,7 +2530,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2541,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2555,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2569,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2583,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2597,7 +2600,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2611,7 +2614,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2625,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2639,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2653,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2667,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2681,7 +2684,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2695,7 +2698,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2709,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2723,7 +2726,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2737,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2751,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2765,7 +2768,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2779,7 +2782,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2793,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2807,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,10 +2821,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,10 +2835,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2849,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2863,7 +2866,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,10 +2877,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2891,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2905,7 +2908,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2919,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2933,7 +2936,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2947,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2961,7 +2964,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2975,7 +2978,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2989,7 +2992,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3003,7 +3006,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,10 +3017,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,10 +3031,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,10 +3045,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3059,7 +3062,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3073,7 +3076,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3087,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3101,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3115,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3129,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3143,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3157,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3171,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3185,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3199,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3213,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3227,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3241,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>351</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3269,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3283,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3297,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3311,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,10 +3325,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3339,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3353,7 +3356,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3367,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3381,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3395,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3409,7 +3412,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3423,7 +3426,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3437,7 +3440,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3448,10 +3451,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3462,10 +3465,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3479,7 +3482,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,10 +3493,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3504,10 +3507,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,10 +3521,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3535,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3549,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3563,7 +3566,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,10 +3577,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3591,7 +3594,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3605,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3619,7 +3622,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3633,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3647,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3661,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3675,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3689,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3703,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3717,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3731,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,10 +3745,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3759,7 +3762,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3773,7 +3776,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3787,7 +3790,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3801,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3812,10 +3815,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3826,10 +3829,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3843,7 +3846,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3857,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3871,7 +3874,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3885,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3899,7 +3902,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3913,7 +3916,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3927,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3941,7 +3944,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3955,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3969,7 +3972,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3983,7 +3986,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3994,10 +3997,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4011,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4025,7 +4028,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4039,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4053,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4064,10 +4067,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4081,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4095,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,7 +4112,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4123,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4137,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4151,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4165,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4179,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4193,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4207,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4221,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4235,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4249,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4263,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,10 +4277,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4291,7 +4294,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4302,10 +4305,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4319,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4333,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4347,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4361,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4375,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4389,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4403,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4417,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4431,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4445,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4459,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4473,7 +4476,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4487,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4501,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4515,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4529,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4543,7 +4546,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4557,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,7 +4574,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4585,7 +4588,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4599,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4613,7 +4616,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4627,7 +4630,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4641,7 +4644,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4655,7 +4658,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4669,7 +4672,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4697,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4711,7 +4714,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4725,7 +4728,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4739,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4753,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4767,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4781,7 +4784,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4795,7 +4798,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,10 +4809,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4823,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4837,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>455</v>
+        <v>275</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4851,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4865,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>457</v>
+        <v>354</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4879,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4893,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>273</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4907,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4921,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>460</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4946,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>462</v>
@@ -4960,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
         <v>463</v>
@@ -5047,7 +5050,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5061,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5075,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5089,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5103,7 +5106,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5117,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5131,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5145,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>269</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5159,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5173,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5187,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5201,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5215,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>476</v>
+        <v>275</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5229,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>354</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5243,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5257,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5271,7 +5274,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5285,7 +5288,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5299,7 +5302,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5313,7 +5316,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5327,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5341,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5355,7 +5358,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5369,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5383,7 +5386,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5397,7 +5400,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>488</v>
+        <v>393</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5411,7 +5414,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5425,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
